--- a/excel-validation/Doordash_Synthetic_Performance_Dataset_days-added.xlsx
+++ b/excel-validation/Doordash_Synthetic_Performance_Dataset_days-added.xlsx
@@ -8,31 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\defaultuser0\Documents\nicosys-portfolio-operations-dash\excel-validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{231B689A-8BE7-4366-AB09-704C3F94084E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579E4447-F3E1-4C7F-A75F-EF6D4ECE4924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="3" activeTab="3" xr2:uid="{6F76AFDF-4A9B-475D-A4BF-90421F07DB89}"/>
+    <workbookView xWindow="10200" yWindow="1524" windowWidth="12840" windowHeight="12156" firstSheet="6" activeTab="6" xr2:uid="{6F76AFDF-4A9B-475D-A4BF-90421F07DB89}"/>
   </bookViews>
   <sheets>
-    <sheet name="avg_earnings_shift_type_day" sheetId="5" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Money_by_day" sheetId="4" r:id="rId3"/>
-    <sheet name="zone_earnings_by_busy_days" sheetId="8" r:id="rId4"/>
-    <sheet name="Doordash_Synthetic_Performance_" sheetId="1" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId6"/>
+    <sheet name="hrs_dollars_per_shift" sheetId="10" r:id="rId1"/>
+    <sheet name="dollar_per_mile" sheetId="9" r:id="rId2"/>
+    <sheet name="avg_earnings_shift_type_day" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
+    <sheet name="Money_by_day" sheetId="4" r:id="rId5"/>
+    <sheet name="zone_earnings_by_busy_days" sheetId="8" r:id="rId6"/>
+    <sheet name="Doordash_Synthetic_Performance_" sheetId="1" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Doordash_Synthetic_Performance_!$A$1:$N$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Doordash_Synthetic_Performance_!$A$1:$N$119</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId7"/>
-    <pivotCache cacheId="11" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="70">
   <si>
     <t>shift_date</t>
   </si>
@@ -231,13 +246,25 @@
   <si>
     <t>Shift Type by Day</t>
   </si>
+  <si>
+    <t>Average of avg_dollars_per_mile</t>
+  </si>
+  <si>
+    <t>Max of avg_dollars_per_mile</t>
+  </si>
+  <si>
+    <t>Min of avg_dollars_per_mile</t>
+  </si>
+  <si>
+    <t>Sum of hours_worked</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -726,17 +753,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -782,12 +811,9 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -805,7 +831,16 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -887,9 +922,129 @@
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:N119" sheet="Doordash_Synthetic_Performance_"/>
   </cacheSource>
-  <cacheFields count="14">
+  <cacheFields count="17">
     <cacheField name="shift_date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-11-03T00:00:00" maxDate="2026-07-20T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-11-03T00:00:00" maxDate="2026-07-20T00:00:00" count="118">
+        <d v="2025-11-03T00:00:00"/>
+        <d v="2025-11-06T00:00:00"/>
+        <d v="2025-11-07T00:00:00"/>
+        <d v="2025-11-08T00:00:00"/>
+        <d v="2025-11-09T00:00:00"/>
+        <d v="2025-11-14T00:00:00"/>
+        <d v="2025-11-15T00:00:00"/>
+        <d v="2025-11-16T00:00:00"/>
+        <d v="2025-11-21T00:00:00"/>
+        <d v="2025-11-22T00:00:00"/>
+        <d v="2025-11-23T00:00:00"/>
+        <d v="2025-11-30T00:00:00"/>
+        <d v="2025-12-02T00:00:00"/>
+        <d v="2025-12-03T00:00:00"/>
+        <d v="2025-12-05T00:00:00"/>
+        <d v="2025-12-06T00:00:00"/>
+        <d v="2025-12-07T00:00:00"/>
+        <d v="2025-12-09T00:00:00"/>
+        <d v="2025-12-13T00:00:00"/>
+        <d v="2025-12-14T00:00:00"/>
+        <d v="2025-12-19T00:00:00"/>
+        <d v="2025-12-20T00:00:00"/>
+        <d v="2025-12-21T00:00:00"/>
+        <d v="2025-12-27T00:00:00"/>
+        <d v="2025-12-28T00:00:00"/>
+        <d v="2025-12-30T00:00:00"/>
+        <d v="2025-12-31T00:00:00"/>
+        <d v="2026-01-03T00:00:00"/>
+        <d v="2026-01-04T00:00:00"/>
+        <d v="2026-01-08T00:00:00"/>
+        <d v="2026-01-09T00:00:00"/>
+        <d v="2026-01-11T00:00:00"/>
+        <d v="2026-01-15T00:00:00"/>
+        <d v="2026-01-24T00:00:00"/>
+        <d v="2026-01-25T00:00:00"/>
+        <d v="2026-01-30T00:00:00"/>
+        <d v="2026-01-31T00:00:00"/>
+        <d v="2026-02-06T00:00:00"/>
+        <d v="2026-02-07T00:00:00"/>
+        <d v="2026-02-08T00:00:00"/>
+        <d v="2026-02-09T00:00:00"/>
+        <d v="2026-02-11T00:00:00"/>
+        <d v="2026-02-13T00:00:00"/>
+        <d v="2026-02-15T00:00:00"/>
+        <d v="2026-02-20T00:00:00"/>
+        <d v="2026-02-21T00:00:00"/>
+        <d v="2026-02-23T00:00:00"/>
+        <d v="2026-02-27T00:00:00"/>
+        <d v="2026-03-01T00:00:00"/>
+        <d v="2026-03-05T00:00:00"/>
+        <d v="2026-03-06T00:00:00"/>
+        <d v="2026-03-07T00:00:00"/>
+        <d v="2026-03-08T00:00:00"/>
+        <d v="2026-03-11T00:00:00"/>
+        <d v="2026-03-13T00:00:00"/>
+        <d v="2026-03-14T00:00:00"/>
+        <d v="2026-03-15T00:00:00"/>
+        <d v="2026-03-19T00:00:00"/>
+        <d v="2026-03-20T00:00:00"/>
+        <d v="2026-03-21T00:00:00"/>
+        <d v="2026-03-22T00:00:00"/>
+        <d v="2026-03-26T00:00:00"/>
+        <d v="2026-03-27T00:00:00"/>
+        <d v="2026-03-28T00:00:00"/>
+        <d v="2026-03-29T00:00:00"/>
+        <d v="2026-04-05T00:00:00"/>
+        <d v="2026-04-09T00:00:00"/>
+        <d v="2026-04-11T00:00:00"/>
+        <d v="2026-04-14T00:00:00"/>
+        <d v="2026-04-15T00:00:00"/>
+        <d v="2026-04-17T00:00:00"/>
+        <d v="2026-04-18T00:00:00"/>
+        <d v="2026-04-19T00:00:00"/>
+        <d v="2026-04-20T00:00:00"/>
+        <d v="2026-04-22T00:00:00"/>
+        <d v="2026-04-23T00:00:00"/>
+        <d v="2026-04-24T00:00:00"/>
+        <d v="2026-04-26T00:00:00"/>
+        <d v="2026-04-29T00:00:00"/>
+        <d v="2026-04-30T00:00:00"/>
+        <d v="2026-05-01T00:00:00"/>
+        <d v="2026-05-02T00:00:00"/>
+        <d v="2026-05-03T00:00:00"/>
+        <d v="2026-05-06T00:00:00"/>
+        <d v="2026-05-08T00:00:00"/>
+        <d v="2026-05-09T00:00:00"/>
+        <d v="2026-05-14T00:00:00"/>
+        <d v="2026-05-15T00:00:00"/>
+        <d v="2026-05-21T00:00:00"/>
+        <d v="2026-05-22T00:00:00"/>
+        <d v="2026-05-24T00:00:00"/>
+        <d v="2026-05-26T00:00:00"/>
+        <d v="2026-05-28T00:00:00"/>
+        <d v="2026-05-30T00:00:00"/>
+        <d v="2026-05-31T00:00:00"/>
+        <d v="2026-06-03T00:00:00"/>
+        <d v="2026-06-07T00:00:00"/>
+        <d v="2026-06-10T00:00:00"/>
+        <d v="2026-06-12T00:00:00"/>
+        <d v="2026-06-14T00:00:00"/>
+        <d v="2026-06-16T00:00:00"/>
+        <d v="2026-06-19T00:00:00"/>
+        <d v="2026-06-20T00:00:00"/>
+        <d v="2026-06-21T00:00:00"/>
+        <d v="2026-06-25T00:00:00"/>
+        <d v="2026-06-26T00:00:00"/>
+        <d v="2026-06-27T00:00:00"/>
+        <d v="2026-06-28T00:00:00"/>
+        <d v="2026-06-29T00:00:00"/>
+        <d v="2026-07-01T00:00:00"/>
+        <d v="2026-07-03T00:00:00"/>
+        <d v="2026-07-05T00:00:00"/>
+        <d v="2026-07-10T00:00:00"/>
+        <d v="2026-07-11T00:00:00"/>
+        <d v="2026-07-12T00:00:00"/>
+        <d v="2026-07-17T00:00:00"/>
+        <d v="2026-07-18T00:00:00"/>
+        <d v="2026-07-19T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="16"/>
     </cacheField>
     <cacheField name="shift_type" numFmtId="0">
       <sharedItems count="6">
@@ -959,6 +1114,51 @@
         <s v="Wednesday"/>
       </sharedItems>
     </cacheField>
+    <cacheField name="Months (shift_date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2025-11-03T00:00:00" endDate="2026-07-20T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;11/3/2025"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;7/20/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Quarters (shift_date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="quarters" startDate="2025-11-03T00:00:00" endDate="2026-07-20T00:00:00"/>
+        <groupItems count="6">
+          <s v="&lt;11/3/2025"/>
+          <s v="Qtr1"/>
+          <s v="Qtr2"/>
+          <s v="Qtr3"/>
+          <s v="Qtr4"/>
+          <s v="&gt;7/20/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Years (shift_date)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="years" startDate="2025-11-03T00:00:00" endDate="2026-07-20T00:00:00"/>
+        <groupItems count="4">
+          <s v="&lt;11/3/2025"/>
+          <s v="2025"/>
+          <s v="2026"/>
+          <s v="&gt;7/20/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -2746,7 +2946,7 @@
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="118">
   <r>
-    <d v="2025-11-03T00:00:00"/>
+    <x v="0"/>
     <x v="0"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T00:00:00"/>
@@ -2762,7 +2962,7 @@
     <x v="0"/>
   </r>
   <r>
-    <d v="2025-11-06T00:00:00"/>
+    <x v="1"/>
     <x v="1"/>
     <d v="1899-12-30T10:45:00"/>
     <d v="1899-12-30T17:00:00"/>
@@ -2778,7 +2978,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2025-11-07T00:00:00"/>
+    <x v="2"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -2794,7 +2994,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2025-11-08T00:00:00"/>
+    <x v="3"/>
     <x v="3"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T22:30:00"/>
@@ -2810,7 +3010,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2025-11-09T00:00:00"/>
+    <x v="4"/>
     <x v="4"/>
     <d v="1899-12-30T14:30:00"/>
     <d v="1899-12-30T20:00:00"/>
@@ -2826,7 +3026,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-11-14T00:00:00"/>
+    <x v="5"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T01:15:00"/>
@@ -2842,7 +3042,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2025-11-15T00:00:00"/>
+    <x v="6"/>
     <x v="3"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T22:45:00"/>
@@ -2858,7 +3058,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2025-11-16T00:00:00"/>
+    <x v="7"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T00:00:00"/>
@@ -2874,7 +3074,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-11-21T00:00:00"/>
+    <x v="8"/>
     <x v="3"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T23:15:00"/>
@@ -2890,7 +3090,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2025-11-22T00:00:00"/>
+    <x v="9"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T23:45:00"/>
@@ -2906,7 +3106,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2025-11-23T00:00:00"/>
+    <x v="10"/>
     <x v="0"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T22:45:00"/>
@@ -2922,7 +3122,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-11-30T00:00:00"/>
+    <x v="11"/>
     <x v="2"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T00:15:00"/>
@@ -2938,7 +3138,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-12-02T00:00:00"/>
+    <x v="12"/>
     <x v="4"/>
     <d v="1899-12-30T15:00:00"/>
     <d v="1899-12-30T21:00:00"/>
@@ -2954,7 +3154,7 @@
     <x v="5"/>
   </r>
   <r>
-    <d v="2025-12-03T00:00:00"/>
+    <x v="13"/>
     <x v="4"/>
     <d v="1899-12-30T14:30:00"/>
     <d v="1899-12-30T20:30:00"/>
@@ -2970,7 +3170,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2025-12-05T00:00:00"/>
+    <x v="14"/>
     <x v="3"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T22:00:00"/>
@@ -2986,7 +3186,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2025-12-06T00:00:00"/>
+    <x v="15"/>
     <x v="2"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T23:30:00"/>
@@ -3002,7 +3202,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2025-12-07T00:00:00"/>
+    <x v="16"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T22:30:00"/>
@@ -3018,7 +3218,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-12-09T00:00:00"/>
+    <x v="17"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T23:30:00"/>
@@ -3034,7 +3234,7 @@
     <x v="5"/>
   </r>
   <r>
-    <d v="2025-12-13T00:00:00"/>
+    <x v="18"/>
     <x v="2"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T00:15:00"/>
@@ -3050,7 +3250,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2025-12-14T00:00:00"/>
+    <x v="19"/>
     <x v="4"/>
     <d v="1899-12-30T15:00:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -3066,7 +3266,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-12-19T00:00:00"/>
+    <x v="20"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T23:15:00"/>
@@ -3082,7 +3282,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2025-12-20T00:00:00"/>
+    <x v="21"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T01:15:00"/>
@@ -3098,7 +3298,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2025-12-21T00:00:00"/>
+    <x v="22"/>
     <x v="0"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T00:15:00"/>
@@ -3114,7 +3314,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-12-27T00:00:00"/>
+    <x v="23"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T00:00:00"/>
@@ -3130,7 +3330,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2025-12-28T00:00:00"/>
+    <x v="24"/>
     <x v="2"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T00:30:00"/>
@@ -3146,7 +3346,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2025-12-30T00:00:00"/>
+    <x v="25"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T22:45:00"/>
@@ -3162,7 +3362,7 @@
     <x v="5"/>
   </r>
   <r>
-    <d v="2025-12-31T00:00:00"/>
+    <x v="26"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T00:00:00"/>
@@ -3178,7 +3378,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-01-03T00:00:00"/>
+    <x v="27"/>
     <x v="3"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T23:15:00"/>
@@ -3194,7 +3394,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-01-04T00:00:00"/>
+    <x v="28"/>
     <x v="2"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T22:30:00"/>
@@ -3210,7 +3410,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-01-08T00:00:00"/>
+    <x v="29"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T22:00:00"/>
@@ -3226,7 +3426,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-01-09T00:00:00"/>
+    <x v="30"/>
     <x v="3"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T22:00:00"/>
@@ -3242,7 +3442,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-01-11T00:00:00"/>
+    <x v="31"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T21:30:00"/>
@@ -3258,7 +3458,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-01-15T00:00:00"/>
+    <x v="32"/>
     <x v="0"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:45:00"/>
@@ -3274,7 +3474,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-01-24T00:00:00"/>
+    <x v="33"/>
     <x v="0"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T22:30:00"/>
@@ -3290,7 +3490,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-01-25T00:00:00"/>
+    <x v="34"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T23:00:00"/>
@@ -3306,7 +3506,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-01-30T00:00:00"/>
+    <x v="35"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -3322,7 +3522,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-01-31T00:00:00"/>
+    <x v="36"/>
     <x v="2"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -3338,7 +3538,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-02-06T00:00:00"/>
+    <x v="37"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T22:00:00"/>
@@ -3354,7 +3554,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-02-07T00:00:00"/>
+    <x v="38"/>
     <x v="3"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T23:15:00"/>
@@ -3370,7 +3570,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-02-08T00:00:00"/>
+    <x v="39"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:45:00"/>
@@ -3386,7 +3586,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-02-09T00:00:00"/>
+    <x v="40"/>
     <x v="3"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T22:45:00"/>
@@ -3402,7 +3602,7 @@
     <x v="0"/>
   </r>
   <r>
-    <d v="2026-02-11T00:00:00"/>
+    <x v="41"/>
     <x v="1"/>
     <d v="1899-12-30T11:15:00"/>
     <d v="1899-12-30T17:30:00"/>
@@ -3418,7 +3618,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-02-13T00:00:00"/>
+    <x v="42"/>
     <x v="3"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T22:15:00"/>
@@ -3434,7 +3634,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-02-15T00:00:00"/>
+    <x v="43"/>
     <x v="2"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T22:30:00"/>
@@ -3450,7 +3650,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-02-20T00:00:00"/>
+    <x v="44"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T23:15:00"/>
@@ -3466,7 +3666,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-02-21T00:00:00"/>
+    <x v="45"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:45:00"/>
@@ -3482,7 +3682,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-02-23T00:00:00"/>
+    <x v="46"/>
     <x v="1"/>
     <d v="1899-12-30T11:00:00"/>
     <d v="1899-12-30T16:00:00"/>
@@ -3498,7 +3698,7 @@
     <x v="0"/>
   </r>
   <r>
-    <d v="2026-02-27T00:00:00"/>
+    <x v="47"/>
     <x v="2"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T21:30:00"/>
@@ -3514,7 +3714,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-03-01T00:00:00"/>
+    <x v="48"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T23:45:00"/>
@@ -3530,7 +3730,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-03-05T00:00:00"/>
+    <x v="49"/>
     <x v="1"/>
     <d v="1899-12-30T10:45:00"/>
     <d v="1899-12-30T15:15:00"/>
@@ -3546,7 +3746,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-03-06T00:00:00"/>
+    <x v="50"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T22:15:00"/>
@@ -3562,7 +3762,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-03-07T00:00:00"/>
+    <x v="51"/>
     <x v="2"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:30:00"/>
@@ -3578,7 +3778,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-03-08T00:00:00"/>
+    <x v="52"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -3594,7 +3794,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-03-11T00:00:00"/>
+    <x v="53"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T00:00:00"/>
@@ -3610,7 +3810,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-03-13T00:00:00"/>
+    <x v="54"/>
     <x v="2"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -3626,7 +3826,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-03-14T00:00:00"/>
+    <x v="55"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T20:30:00"/>
@@ -3642,7 +3842,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-03-15T00:00:00"/>
+    <x v="56"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -3658,7 +3858,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-03-19T00:00:00"/>
+    <x v="57"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:00:00"/>
@@ -3674,7 +3874,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-03-20T00:00:00"/>
+    <x v="58"/>
     <x v="0"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:00:00"/>
@@ -3690,7 +3890,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-03-21T00:00:00"/>
+    <x v="59"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:00:00"/>
@@ -3706,7 +3906,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-03-22T00:00:00"/>
+    <x v="60"/>
     <x v="2"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T20:45:00"/>
@@ -3722,7 +3922,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-03-26T00:00:00"/>
+    <x v="61"/>
     <x v="3"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T19:00:00"/>
@@ -3738,7 +3938,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-03-27T00:00:00"/>
+    <x v="62"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:45:00"/>
@@ -3754,7 +3954,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-03-28T00:00:00"/>
+    <x v="63"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T21:15:00"/>
@@ -3770,7 +3970,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-03-29T00:00:00"/>
+    <x v="64"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:00:00"/>
@@ -3786,7 +3986,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-04-05T00:00:00"/>
+    <x v="65"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T21:30:00"/>
@@ -3802,7 +4002,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-04-09T00:00:00"/>
+    <x v="66"/>
     <x v="0"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T19:30:00"/>
@@ -3818,7 +4018,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-04-11T00:00:00"/>
+    <x v="67"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -3834,7 +4034,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-04-14T00:00:00"/>
+    <x v="68"/>
     <x v="5"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T21:15:00"/>
@@ -3850,7 +4050,7 @@
     <x v="5"/>
   </r>
   <r>
-    <d v="2026-04-15T00:00:00"/>
+    <x v="69"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:15:00"/>
@@ -3866,7 +4066,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-04-17T00:00:00"/>
+    <x v="70"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T21:30:00"/>
@@ -3882,7 +4082,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-04-18T00:00:00"/>
+    <x v="71"/>
     <x v="2"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T19:45:00"/>
@@ -3898,7 +4098,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-04-19T00:00:00"/>
+    <x v="72"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T21:45:00"/>
@@ -3914,7 +4114,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-04-20T00:00:00"/>
+    <x v="73"/>
     <x v="1"/>
     <d v="1899-12-30T11:15:00"/>
     <d v="1899-12-30T15:45:00"/>
@@ -3930,7 +4130,7 @@
     <x v="0"/>
   </r>
   <r>
-    <d v="2026-04-22T00:00:00"/>
+    <x v="74"/>
     <x v="1"/>
     <d v="1899-12-30T11:15:00"/>
     <d v="1899-12-30T15:00:00"/>
@@ -3946,7 +4146,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-04-23T00:00:00"/>
+    <x v="75"/>
     <x v="5"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T21:30:00"/>
@@ -3962,7 +4162,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-04-24T00:00:00"/>
+    <x v="76"/>
     <x v="2"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -3978,7 +4178,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-04-26T00:00:00"/>
+    <x v="77"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:15:00"/>
@@ -3994,7 +4194,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-04-29T00:00:00"/>
+    <x v="78"/>
     <x v="1"/>
     <d v="1899-12-30T11:00:00"/>
     <d v="1899-12-30T15:30:00"/>
@@ -4010,7 +4210,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-04-30T00:00:00"/>
+    <x v="79"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T23:15:00"/>
@@ -4026,7 +4226,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-05-01T00:00:00"/>
+    <x v="80"/>
     <x v="0"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:00:00"/>
@@ -4042,7 +4242,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-05-02T00:00:00"/>
+    <x v="81"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -4058,7 +4258,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-05-03T00:00:00"/>
+    <x v="82"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:00:00"/>
@@ -4074,7 +4274,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-05-06T00:00:00"/>
+    <x v="83"/>
     <x v="1"/>
     <d v="1899-12-30T11:15:00"/>
     <d v="1899-12-30T14:45:00"/>
@@ -4090,7 +4290,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-05-08T00:00:00"/>
+    <x v="84"/>
     <x v="2"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -4106,7 +4306,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-05-09T00:00:00"/>
+    <x v="85"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T21:00:00"/>
@@ -4122,7 +4322,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-05-14T00:00:00"/>
+    <x v="86"/>
     <x v="5"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:45:00"/>
@@ -4138,7 +4338,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-05-15T00:00:00"/>
+    <x v="87"/>
     <x v="0"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T23:00:00"/>
@@ -4154,7 +4354,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-05-21T00:00:00"/>
+    <x v="88"/>
     <x v="3"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:30:00"/>
@@ -4170,7 +4370,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-05-22T00:00:00"/>
+    <x v="89"/>
     <x v="5"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:00:00"/>
@@ -4186,7 +4386,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-05-24T00:00:00"/>
+    <x v="90"/>
     <x v="3"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:15:00"/>
@@ -4202,7 +4402,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-05-26T00:00:00"/>
+    <x v="91"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:30:00"/>
@@ -4218,7 +4418,7 @@
     <x v="5"/>
   </r>
   <r>
-    <d v="2026-05-28T00:00:00"/>
+    <x v="92"/>
     <x v="1"/>
     <d v="1899-12-30T11:30:00"/>
     <d v="1899-12-30T14:45:00"/>
@@ -4234,7 +4434,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-05-30T00:00:00"/>
+    <x v="93"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -4250,7 +4450,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-05-31T00:00:00"/>
+    <x v="94"/>
     <x v="2"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T18:45:00"/>
@@ -4266,7 +4466,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-06-03T00:00:00"/>
+    <x v="95"/>
     <x v="3"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -4282,7 +4482,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-06-07T00:00:00"/>
+    <x v="96"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T19:45:00"/>
@@ -4298,7 +4498,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-06-10T00:00:00"/>
+    <x v="97"/>
     <x v="5"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T19:15:00"/>
@@ -4314,7 +4514,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-06-12T00:00:00"/>
+    <x v="98"/>
     <x v="3"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:00:00"/>
@@ -4330,7 +4530,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-06-14T00:00:00"/>
+    <x v="99"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:30:00"/>
@@ -4346,7 +4546,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-06-16T00:00:00"/>
+    <x v="100"/>
     <x v="5"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:45:00"/>
@@ -4362,7 +4562,7 @@
     <x v="5"/>
   </r>
   <r>
-    <d v="2026-06-19T00:00:00"/>
+    <x v="101"/>
     <x v="2"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:45:00"/>
@@ -4378,7 +4578,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-06-20T00:00:00"/>
+    <x v="102"/>
     <x v="0"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -4394,7 +4594,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-06-21T00:00:00"/>
+    <x v="103"/>
     <x v="2"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:30:00"/>
@@ -4410,7 +4610,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-06-25T00:00:00"/>
+    <x v="104"/>
     <x v="0"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T20:15:00"/>
@@ -4426,7 +4626,7 @@
     <x v="1"/>
   </r>
   <r>
-    <d v="2026-06-26T00:00:00"/>
+    <x v="105"/>
     <x v="3"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T19:15:00"/>
@@ -4442,7 +4642,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-06-27T00:00:00"/>
+    <x v="106"/>
     <x v="3"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:00:00"/>
@@ -4458,7 +4658,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-06-28T00:00:00"/>
+    <x v="107"/>
     <x v="2"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:15:00"/>
@@ -4474,7 +4674,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-06-29T00:00:00"/>
+    <x v="108"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T22:15:00"/>
@@ -4490,7 +4690,7 @@
     <x v="0"/>
   </r>
   <r>
-    <d v="2026-07-01T00:00:00"/>
+    <x v="109"/>
     <x v="3"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T21:00:00"/>
@@ -4506,7 +4706,7 @@
     <x v="6"/>
   </r>
   <r>
-    <d v="2026-07-03T00:00:00"/>
+    <x v="110"/>
     <x v="0"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T20:30:00"/>
@@ -4522,7 +4722,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-07-05T00:00:00"/>
+    <x v="111"/>
     <x v="2"/>
     <d v="1899-12-30T16:00:00"/>
     <d v="1899-12-30T19:45:00"/>
@@ -4538,7 +4738,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-07-10T00:00:00"/>
+    <x v="112"/>
     <x v="0"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T20:00:00"/>
@@ -4554,7 +4754,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-07-11T00:00:00"/>
+    <x v="113"/>
     <x v="3"/>
     <d v="1899-12-30T16:30:00"/>
     <d v="1899-12-30T19:30:00"/>
@@ -4570,7 +4770,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-07-12T00:00:00"/>
+    <x v="114"/>
     <x v="3"/>
     <d v="1899-12-30T17:00:00"/>
     <d v="1899-12-30T19:45:00"/>
@@ -4586,7 +4786,7 @@
     <x v="4"/>
   </r>
   <r>
-    <d v="2026-07-17T00:00:00"/>
+    <x v="115"/>
     <x v="5"/>
     <d v="1899-12-30T18:00:00"/>
     <d v="1899-12-30T22:00:00"/>
@@ -4602,7 +4802,7 @@
     <x v="2"/>
   </r>
   <r>
-    <d v="2026-07-18T00:00:00"/>
+    <x v="116"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T20:30:00"/>
@@ -4618,7 +4818,7 @@
     <x v="3"/>
   </r>
   <r>
-    <d v="2026-07-19T00:00:00"/>
+    <x v="117"/>
     <x v="0"/>
     <d v="1899-12-30T17:30:00"/>
     <d v="1899-12-30T21:00:00"/>
@@ -4637,10 +4837,1240 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2AED747C-F735-4A03-8FD8-66CD5EE5BF4A}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Shift Type by Day">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C418CD9-D649-46D1-BEED-35F8A35CDD48}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C122" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="17">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="119">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="21" showAll="0"/>
+    <pivotField numFmtId="21" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="119">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="106"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="113"/>
+    </i>
+    <i>
+      <x v="114"/>
+    </i>
+    <i>
+      <x v="115"/>
+    </i>
+    <i>
+      <x v="116"/>
+    </i>
+    <i>
+      <x v="117"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of hours_worked" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Sum of gross_earnings" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <conditionalFormats count="2">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="0" count="118">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+              <x v="31"/>
+              <x v="32"/>
+              <x v="33"/>
+              <x v="34"/>
+              <x v="35"/>
+              <x v="36"/>
+              <x v="37"/>
+              <x v="38"/>
+              <x v="39"/>
+              <x v="40"/>
+              <x v="41"/>
+              <x v="42"/>
+              <x v="43"/>
+              <x v="44"/>
+              <x v="45"/>
+              <x v="46"/>
+              <x v="47"/>
+              <x v="48"/>
+              <x v="49"/>
+              <x v="50"/>
+              <x v="51"/>
+              <x v="52"/>
+              <x v="53"/>
+              <x v="54"/>
+              <x v="55"/>
+              <x v="56"/>
+              <x v="57"/>
+              <x v="58"/>
+              <x v="59"/>
+              <x v="60"/>
+              <x v="61"/>
+              <x v="62"/>
+              <x v="63"/>
+              <x v="64"/>
+              <x v="65"/>
+              <x v="66"/>
+              <x v="67"/>
+              <x v="68"/>
+              <x v="69"/>
+              <x v="70"/>
+              <x v="71"/>
+              <x v="72"/>
+              <x v="73"/>
+              <x v="74"/>
+              <x v="75"/>
+              <x v="76"/>
+              <x v="77"/>
+              <x v="78"/>
+              <x v="79"/>
+              <x v="80"/>
+              <x v="81"/>
+              <x v="82"/>
+              <x v="83"/>
+              <x v="84"/>
+              <x v="85"/>
+              <x v="86"/>
+              <x v="87"/>
+              <x v="88"/>
+              <x v="89"/>
+              <x v="90"/>
+              <x v="91"/>
+              <x v="92"/>
+              <x v="93"/>
+              <x v="94"/>
+              <x v="95"/>
+              <x v="96"/>
+              <x v="97"/>
+              <x v="98"/>
+              <x v="99"/>
+              <x v="100"/>
+              <x v="101"/>
+              <x v="102"/>
+              <x v="103"/>
+              <x v="104"/>
+              <x v="105"/>
+              <x v="106"/>
+              <x v="107"/>
+              <x v="108"/>
+              <x v="109"/>
+              <x v="110"/>
+              <x v="111"/>
+              <x v="112"/>
+              <x v="113"/>
+              <x v="114"/>
+              <x v="115"/>
+              <x v="116"/>
+              <x v="117"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="0" count="118">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+              <x v="31"/>
+              <x v="32"/>
+              <x v="33"/>
+              <x v="34"/>
+              <x v="35"/>
+              <x v="36"/>
+              <x v="37"/>
+              <x v="38"/>
+              <x v="39"/>
+              <x v="40"/>
+              <x v="41"/>
+              <x v="42"/>
+              <x v="43"/>
+              <x v="44"/>
+              <x v="45"/>
+              <x v="46"/>
+              <x v="47"/>
+              <x v="48"/>
+              <x v="49"/>
+              <x v="50"/>
+              <x v="51"/>
+              <x v="52"/>
+              <x v="53"/>
+              <x v="54"/>
+              <x v="55"/>
+              <x v="56"/>
+              <x v="57"/>
+              <x v="58"/>
+              <x v="59"/>
+              <x v="60"/>
+              <x v="61"/>
+              <x v="62"/>
+              <x v="63"/>
+              <x v="64"/>
+              <x v="65"/>
+              <x v="66"/>
+              <x v="67"/>
+              <x v="68"/>
+              <x v="69"/>
+              <x v="70"/>
+              <x v="71"/>
+              <x v="72"/>
+              <x v="73"/>
+              <x v="74"/>
+              <x v="75"/>
+              <x v="76"/>
+              <x v="77"/>
+              <x v="78"/>
+              <x v="79"/>
+              <x v="80"/>
+              <x v="81"/>
+              <x v="82"/>
+              <x v="83"/>
+              <x v="84"/>
+              <x v="85"/>
+              <x v="86"/>
+              <x v="87"/>
+              <x v="88"/>
+              <x v="89"/>
+              <x v="90"/>
+              <x v="91"/>
+              <x v="92"/>
+              <x v="93"/>
+              <x v="94"/>
+              <x v="95"/>
+              <x v="96"/>
+              <x v="97"/>
+              <x v="98"/>
+              <x v="99"/>
+              <x v="100"/>
+              <x v="101"/>
+              <x v="102"/>
+              <x v="103"/>
+              <x v="104"/>
+              <x v="105"/>
+              <x v="106"/>
+              <x v="107"/>
+              <x v="108"/>
+              <x v="109"/>
+              <x v="110"/>
+              <x v="111"/>
+              <x v="112"/>
+              <x v="113"/>
+              <x v="114"/>
+              <x v="115"/>
+              <x v="116"/>
+              <x v="117"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{42081264-8E89-4580-90C4-633D3404317A}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C4" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="17">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="119">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="21" showAll="0"/>
+    <pivotField numFmtId="21" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="8">
+        <item x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Average of avg_dollars_per_mile" fld="8" subtotal="average" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Max of avg_dollars_per_mile" fld="8" subtotal="max" baseField="0" baseItem="1" numFmtId="164"/>
+    <dataField name="Min of avg_dollars_per_mile" fld="8" subtotal="min" baseField="0" baseItem="1" numFmtId="164"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2" selected="0">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2AED747C-F735-4A03-8FD8-66CD5EE5BF4A}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Shift Type by Day">
   <location ref="A3:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0"/>
+  <pivotFields count="17">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="119">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="7">
         <item x="0"/>
@@ -4693,6 +6123,45 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="2">
     <field x="13"/>
@@ -4752,17 +6221,17 @@
     <dataField name="Average of gross_earnings" fld="5" subtotal="average" baseField="1" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="0">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="6">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -4771,7 +6240,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="4">
@@ -4786,7 +6255,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -4795,7 +6264,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="4">
@@ -4810,7 +6279,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="13" count="1">
@@ -4819,7 +6288,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="3">
@@ -4846,8 +6315,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED6CB9C1-917E-47E4-81A6-56612A90C1D2}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Days of Week">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED6CB9C1-917E-47E4-81A6-56612A90C1D2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Days of Week">
   <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField numFmtId="14" showAll="0"/>
@@ -4922,11 +6391,133 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AAD2FB8-DE7E-4294-8A5A-5D8E04940887}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8AAD2FB8-DE7E-4294-8A5A-5D8E04940887}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0"/>
+  <pivotFields count="17">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="119">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField numFmtId="21" showAll="0"/>
     <pivotField numFmtId="21" showAll="0"/>
@@ -4960,6 +6551,45 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="1">
     <field x="13"/>
@@ -5008,11 +6638,133 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8324A8DF-0B41-471A-A6C2-3402DE705759}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8324A8DF-0B41-471A-A6C2-3402DE705759}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0"/>
+  <pivotFields count="17">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="119">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField numFmtId="21" showAll="0"/>
     <pivotField numFmtId="21" showAll="0"/>
@@ -5050,6 +6802,45 @@
         <item h="1" x="5"/>
         <item h="1" x="6"/>
         <item h="1" x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item t="default"/>
@@ -5459,6 +7250,1396 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91511D34-9BCB-4641-AB9A-4F3D7F0F3CD8}">
+  <dimension ref="A3:C122"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>45964</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>70.739999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>45967</v>
+      </c>
+      <c r="B5">
+        <v>6.25</v>
+      </c>
+      <c r="C5">
+        <v>64.67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>45968</v>
+      </c>
+      <c r="B6">
+        <v>5.25</v>
+      </c>
+      <c r="C6">
+        <v>52.87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>45969</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>43.73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>45970</v>
+      </c>
+      <c r="B8">
+        <v>5.5</v>
+      </c>
+      <c r="C8">
+        <v>44.78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>45975</v>
+      </c>
+      <c r="B9">
+        <v>7.75</v>
+      </c>
+      <c r="C9">
+        <v>70.59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>45976</v>
+      </c>
+      <c r="B10">
+        <v>6.75</v>
+      </c>
+      <c r="C10">
+        <v>75.849999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>45977</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>59.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>45982</v>
+      </c>
+      <c r="B12">
+        <v>6.75</v>
+      </c>
+      <c r="C12">
+        <v>74.08</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>45983</v>
+      </c>
+      <c r="B13">
+        <v>5.75</v>
+      </c>
+      <c r="C13">
+        <v>50.13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>45984</v>
+      </c>
+      <c r="B14">
+        <v>6.75</v>
+      </c>
+      <c r="C14">
+        <v>64.209999999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>45991</v>
+      </c>
+      <c r="B15">
+        <v>6.75</v>
+      </c>
+      <c r="C15">
+        <v>45.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>45993</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>45994</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>52.21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>45996</v>
+      </c>
+      <c r="B18">
+        <v>5.5</v>
+      </c>
+      <c r="C18">
+        <v>52.13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>45997</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19">
+        <v>63.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>45998</v>
+      </c>
+      <c r="B20">
+        <v>5.5</v>
+      </c>
+      <c r="C20">
+        <v>57.07</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
+        <v>46000</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>53.45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="9">
+        <v>46004</v>
+      </c>
+      <c r="B22">
+        <v>6.75</v>
+      </c>
+      <c r="C22">
+        <v>50.43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
+        <v>46005</v>
+      </c>
+      <c r="B23">
+        <v>5.25</v>
+      </c>
+      <c r="C23">
+        <v>32.409999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>46010</v>
+      </c>
+      <c r="B24">
+        <v>6.75</v>
+      </c>
+      <c r="C24">
+        <v>69.72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="9">
+        <v>46011</v>
+      </c>
+      <c r="B25">
+        <v>7.25</v>
+      </c>
+      <c r="C25">
+        <v>62.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
+        <v>46012</v>
+      </c>
+      <c r="B26">
+        <v>7.25</v>
+      </c>
+      <c r="C26">
+        <v>89.24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="9">
+        <v>46018</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>46.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="9">
+        <v>46019</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>69.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
+        <v>46021</v>
+      </c>
+      <c r="B29">
+        <v>5.75</v>
+      </c>
+      <c r="C29">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>46022</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>46.67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="9">
+        <v>46025</v>
+      </c>
+      <c r="B31">
+        <v>5.25</v>
+      </c>
+      <c r="C31">
+        <v>77.66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>46026</v>
+      </c>
+      <c r="B32">
+        <v>5.5</v>
+      </c>
+      <c r="C32">
+        <v>54.81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="9">
+        <v>46030</v>
+      </c>
+      <c r="B33">
+        <v>4.5</v>
+      </c>
+      <c r="C33">
+        <v>43.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B34">
+        <v>5.5</v>
+      </c>
+      <c r="C34">
+        <v>61.67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="9">
+        <v>46033</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>53.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="9">
+        <v>46037</v>
+      </c>
+      <c r="B36">
+        <v>4.75</v>
+      </c>
+      <c r="C36">
+        <v>61.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="9">
+        <v>46046</v>
+      </c>
+      <c r="B37">
+        <v>5.5</v>
+      </c>
+      <c r="C37">
+        <v>81.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="9">
+        <v>46047</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>65.27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>46052</v>
+      </c>
+      <c r="B39">
+        <v>5.25</v>
+      </c>
+      <c r="C39">
+        <v>69.89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="9">
+        <v>46053</v>
+      </c>
+      <c r="B40">
+        <v>4.75</v>
+      </c>
+      <c r="C40">
+        <v>60.98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="9">
+        <v>46059</v>
+      </c>
+      <c r="B41">
+        <v>5.5</v>
+      </c>
+      <c r="C41">
+        <v>60.14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="9">
+        <v>46060</v>
+      </c>
+      <c r="B42">
+        <v>5.75</v>
+      </c>
+      <c r="C42">
+        <v>75.569999999999993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="9">
+        <v>46061</v>
+      </c>
+      <c r="B43">
+        <v>4.75</v>
+      </c>
+      <c r="C43">
+        <v>69.27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="9">
+        <v>46062</v>
+      </c>
+      <c r="B44">
+        <v>5.25</v>
+      </c>
+      <c r="C44">
+        <v>81.11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="9">
+        <v>46064</v>
+      </c>
+      <c r="B45">
+        <v>6.25</v>
+      </c>
+      <c r="C45">
+        <v>54.62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="9">
+        <v>46066</v>
+      </c>
+      <c r="B46">
+        <v>5.75</v>
+      </c>
+      <c r="C46">
+        <v>83.89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="9">
+        <v>46068</v>
+      </c>
+      <c r="B47">
+        <v>5.5</v>
+      </c>
+      <c r="C47">
+        <v>54.79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="9">
+        <v>46073</v>
+      </c>
+      <c r="B48">
+        <v>5.25</v>
+      </c>
+      <c r="C48">
+        <v>78.959999999999994</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="9">
+        <v>46074</v>
+      </c>
+      <c r="B49">
+        <v>4.25</v>
+      </c>
+      <c r="C49">
+        <v>53.39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="9">
+        <v>46076</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>58.59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="9">
+        <v>46080</v>
+      </c>
+      <c r="B51">
+        <v>5.5</v>
+      </c>
+      <c r="C51">
+        <v>49.03</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="9">
+        <v>46082</v>
+      </c>
+      <c r="B52">
+        <v>5.75</v>
+      </c>
+      <c r="C52">
+        <v>71.34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="9">
+        <v>46086</v>
+      </c>
+      <c r="B53">
+        <v>4.5</v>
+      </c>
+      <c r="C53">
+        <v>60.07</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="9">
+        <v>46087</v>
+      </c>
+      <c r="B54">
+        <v>5.25</v>
+      </c>
+      <c r="C54">
+        <v>70.239999999999995</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="9">
+        <v>46088</v>
+      </c>
+      <c r="B55">
+        <v>4.5</v>
+      </c>
+      <c r="C55">
+        <v>48.32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="9">
+        <v>46089</v>
+      </c>
+      <c r="B56">
+        <v>5.25</v>
+      </c>
+      <c r="C56">
+        <v>81.709999999999994</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="9">
+        <v>46092</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>65.03</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="9">
+        <v>46094</v>
+      </c>
+      <c r="B58">
+        <v>4.25</v>
+      </c>
+      <c r="C58">
+        <v>72.47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="9">
+        <v>46095</v>
+      </c>
+      <c r="B59">
+        <v>3.5</v>
+      </c>
+      <c r="C59">
+        <v>51.83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="9">
+        <v>46096</v>
+      </c>
+      <c r="B60">
+        <v>4.75</v>
+      </c>
+      <c r="C60">
+        <v>84.44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="9">
+        <v>46100</v>
+      </c>
+      <c r="B61">
+        <v>3.5</v>
+      </c>
+      <c r="C61">
+        <v>55.45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="9">
+        <v>46101</v>
+      </c>
+      <c r="B62">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <v>79.94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="9">
+        <v>46102</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>74.349999999999994</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="9">
+        <v>46103</v>
+      </c>
+      <c r="B64">
+        <v>3.25</v>
+      </c>
+      <c r="C64">
+        <v>58.46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="9">
+        <v>46107</v>
+      </c>
+      <c r="B65">
+        <v>3</v>
+      </c>
+      <c r="C65">
+        <v>42.95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="9">
+        <v>46108</v>
+      </c>
+      <c r="B66">
+        <v>4.75</v>
+      </c>
+      <c r="C66">
+        <v>67.78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="9">
+        <v>46109</v>
+      </c>
+      <c r="B67">
+        <v>4.75</v>
+      </c>
+      <c r="C67">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68">
+        <v>68.92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="9">
+        <v>46117</v>
+      </c>
+      <c r="B69">
+        <v>3.5</v>
+      </c>
+      <c r="C69">
+        <v>62.56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="9">
+        <v>46121</v>
+      </c>
+      <c r="B70">
+        <v>3.5</v>
+      </c>
+      <c r="C70">
+        <v>41.87</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="9">
+        <v>46123</v>
+      </c>
+      <c r="B71">
+        <v>3.75</v>
+      </c>
+      <c r="C71">
+        <v>58.55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B72">
+        <v>4.25</v>
+      </c>
+      <c r="C72">
+        <v>59.95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="9">
+        <v>46127</v>
+      </c>
+      <c r="B73">
+        <v>4.25</v>
+      </c>
+      <c r="C73">
+        <v>63.86</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="9">
+        <v>46129</v>
+      </c>
+      <c r="B74">
+        <v>5</v>
+      </c>
+      <c r="C74">
+        <v>78.84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="9">
+        <v>46130</v>
+      </c>
+      <c r="B75">
+        <v>3.75</v>
+      </c>
+      <c r="C75">
+        <v>67.739999999999995</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="9">
+        <v>46131</v>
+      </c>
+      <c r="B76">
+        <v>4.75</v>
+      </c>
+      <c r="C76">
+        <v>80.13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="9">
+        <v>46132</v>
+      </c>
+      <c r="B77">
+        <v>4.5</v>
+      </c>
+      <c r="C77">
+        <v>80.78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="9">
+        <v>46134</v>
+      </c>
+      <c r="B78">
+        <v>3.75</v>
+      </c>
+      <c r="C78">
+        <v>59.07</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="9">
+        <v>46135</v>
+      </c>
+      <c r="B79">
+        <v>4.5</v>
+      </c>
+      <c r="C79">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="9">
+        <v>46136</v>
+      </c>
+      <c r="B80">
+        <v>4.25</v>
+      </c>
+      <c r="C80">
+        <v>60.94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="9">
+        <v>46138</v>
+      </c>
+      <c r="B81">
+        <v>4.25</v>
+      </c>
+      <c r="C81">
+        <v>84.67</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="9">
+        <v>46141</v>
+      </c>
+      <c r="B82">
+        <v>4.5</v>
+      </c>
+      <c r="C82">
+        <v>62.14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="9">
+        <v>46142</v>
+      </c>
+      <c r="B83">
+        <v>5.25</v>
+      </c>
+      <c r="C83">
+        <v>79.03</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="9">
+        <v>46143</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84">
+        <v>57.61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="9">
+        <v>46144</v>
+      </c>
+      <c r="B85">
+        <v>3.75</v>
+      </c>
+      <c r="C85">
+        <v>59.67</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="9">
+        <v>46145</v>
+      </c>
+      <c r="B86">
+        <v>3.5</v>
+      </c>
+      <c r="C86">
+        <v>64.709999999999994</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="9">
+        <v>46148</v>
+      </c>
+      <c r="B87">
+        <v>3.5</v>
+      </c>
+      <c r="C87">
+        <v>63.18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="9">
+        <v>46150</v>
+      </c>
+      <c r="B88">
+        <v>4.25</v>
+      </c>
+      <c r="C88">
+        <v>80.13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="9">
+        <v>46151</v>
+      </c>
+      <c r="B89">
+        <v>4.5</v>
+      </c>
+      <c r="C89">
+        <v>86.23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="9">
+        <v>46156</v>
+      </c>
+      <c r="B90">
+        <v>4.75</v>
+      </c>
+      <c r="C90">
+        <v>65.739999999999995</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="9">
+        <v>46157</v>
+      </c>
+      <c r="B91">
+        <v>5</v>
+      </c>
+      <c r="C91">
+        <v>91.43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="9">
+        <v>46163</v>
+      </c>
+      <c r="B92">
+        <v>4</v>
+      </c>
+      <c r="C92">
+        <v>85.35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="9">
+        <v>46164</v>
+      </c>
+      <c r="B93">
+        <v>3.5</v>
+      </c>
+      <c r="C93">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="9">
+        <v>46166</v>
+      </c>
+      <c r="B94">
+        <v>3.75</v>
+      </c>
+      <c r="C94">
+        <v>85.23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B95">
+        <v>4</v>
+      </c>
+      <c r="C95">
+        <v>73.05</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="9">
+        <v>46170</v>
+      </c>
+      <c r="B96">
+        <v>3.25</v>
+      </c>
+      <c r="C96">
+        <v>69.63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="9">
+        <v>46172</v>
+      </c>
+      <c r="B97">
+        <v>3.25</v>
+      </c>
+      <c r="C97">
+        <v>59.36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="9">
+        <v>46173</v>
+      </c>
+      <c r="B98">
+        <v>2.75</v>
+      </c>
+      <c r="C98">
+        <v>51.33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="9">
+        <v>46176</v>
+      </c>
+      <c r="B99">
+        <v>3.75</v>
+      </c>
+      <c r="C99">
+        <v>75.55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="9">
+        <v>46180</v>
+      </c>
+      <c r="B100">
+        <v>3.25</v>
+      </c>
+      <c r="C100">
+        <v>63.42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="9">
+        <v>46183</v>
+      </c>
+      <c r="B101">
+        <v>2.75</v>
+      </c>
+      <c r="C101">
+        <v>53.76</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="9">
+        <v>46185</v>
+      </c>
+      <c r="B102">
+        <v>3.5</v>
+      </c>
+      <c r="C102">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="9">
+        <v>46187</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103">
+        <v>76.13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B104">
+        <v>4.75</v>
+      </c>
+      <c r="C104">
+        <v>86.36</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="9">
+        <v>46192</v>
+      </c>
+      <c r="B105">
+        <v>4.25</v>
+      </c>
+      <c r="C105">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="9">
+        <v>46193</v>
+      </c>
+      <c r="B106">
+        <v>3.25</v>
+      </c>
+      <c r="C106">
+        <v>68.41</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="9">
+        <v>46194</v>
+      </c>
+      <c r="B107">
+        <v>4.5</v>
+      </c>
+      <c r="C107">
+        <v>90.49</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="9">
+        <v>46198</v>
+      </c>
+      <c r="B108">
+        <v>3.75</v>
+      </c>
+      <c r="C108">
+        <v>65.010000000000005</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="9">
+        <v>46199</v>
+      </c>
+      <c r="B109">
+        <v>2.75</v>
+      </c>
+      <c r="C109">
+        <v>54.64</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="9">
+        <v>46200</v>
+      </c>
+      <c r="B110">
+        <v>3.5</v>
+      </c>
+      <c r="C110">
+        <v>60.87</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="9">
+        <v>46201</v>
+      </c>
+      <c r="B111">
+        <v>3.75</v>
+      </c>
+      <c r="C111">
+        <v>79.209999999999994</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="9">
+        <v>46202</v>
+      </c>
+      <c r="B112">
+        <v>4.75</v>
+      </c>
+      <c r="C112">
+        <v>95.04</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="9">
+        <v>46204</v>
+      </c>
+      <c r="B113">
+        <v>3</v>
+      </c>
+      <c r="C113">
+        <v>65.66</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="9">
+        <v>46206</v>
+      </c>
+      <c r="B114">
+        <v>4.5</v>
+      </c>
+      <c r="C114">
+        <v>96.44</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="9">
+        <v>46208</v>
+      </c>
+      <c r="B115">
+        <v>3.75</v>
+      </c>
+      <c r="C115">
+        <v>78.03</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="9">
+        <v>46213</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116">
+        <v>58.37</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="9">
+        <v>46214</v>
+      </c>
+      <c r="B117">
+        <v>3</v>
+      </c>
+      <c r="C117">
+        <v>61.89</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="9">
+        <v>46215</v>
+      </c>
+      <c r="B118">
+        <v>2.75</v>
+      </c>
+      <c r="C118">
+        <v>56.87</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="9">
+        <v>46220</v>
+      </c>
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="C119">
+        <v>92.15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="9">
+        <v>46221</v>
+      </c>
+      <c r="B120">
+        <v>3</v>
+      </c>
+      <c r="C120">
+        <v>57.09</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="9">
+        <v>46222</v>
+      </c>
+      <c r="B121">
+        <v>3.5</v>
+      </c>
+      <c r="C121">
+        <v>62.28</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B122">
+        <v>559.75</v>
+      </c>
+      <c r="C122">
+        <v>7769.9299999999994</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting pivot="1" sqref="B4:B121">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C4:C121">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0280637-2516-4226-94A0-9E1057BC83FA}">
+  <dimension ref="A3:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>3.4528813559322047</v>
+      </c>
+      <c r="B4" s="6">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92622D45-E192-4CAD-91C9-9B6A6E307092}">
   <dimension ref="A3:B18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5468,7 +8649,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B3" t="s">
@@ -5476,122 +8657,122 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>70.701851851851842</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>80.675000000000011</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>74.220999999999989</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>68.305000000000007</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>65.564285714285717</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>66.438387096774179</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>70.641428571428577</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>69.747142857142862</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>66.64533333333334</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>38.594999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>63.193599999999996</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>64.064999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>63.344999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>62.608181818181812</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>66.84795180722891</v>
       </c>
     </row>
@@ -5600,7 +8781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9252857E-5429-4472-A1BF-EC4C5C8532AD}">
   <dimension ref="A3:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5610,7 +8791,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B3" t="s">
@@ -5618,66 +8799,66 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>0</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>2059.59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>386.26000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>385.11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>661.74999999999989</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>788.43000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>1908.9500000000003</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>1579.84</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>7769.93</v>
       </c>
     </row>
@@ -5686,7 +8867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{468DB881-8EB4-41D9-896D-4CDE333C8324}">
   <dimension ref="A3:B11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5696,7 +8877,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
@@ -5704,66 +8885,66 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>2059.59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>1908.9500000000003</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>1579.84</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>788.43000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>661.74999999999989</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>386.26000000000005</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>385.11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>7769.93</v>
       </c>
     </row>
@@ -5772,7 +8953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634AFB3A-67CE-4529-8506-CC1842A34868}">
   <dimension ref="A3:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5782,7 +8963,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
@@ -5790,170 +8971,170 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>2228.7800000000002</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>811.43000000000006</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>901.58</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>515.77</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>1165.6199999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>367.08</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>312.3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>486.24</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>800.34</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>441.15</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>237.58</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>121.60999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>777.01</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>274.57</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <v>215.88</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>286.56</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <v>576.63</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <v>165.36</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <v>241.61</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <v>169.66</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <v>5548.3799999999992</v>
       </c>
     </row>
@@ -5962,7 +9143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3D6565-B603-428A-B662-9FB5A2906182}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:N119"/>
@@ -11336,11 +14517,37 @@
       </filters>
     </filterColumn>
   </autoFilter>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="iconSet" priority="3">
+      <iconSet iconSet="5Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="20"/>
+        <cfvo type="percent" val="40"/>
+        <cfvo type="percent" val="60"/>
+        <cfvo type="percent" val="80"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="2">
+      <iconSet>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="4Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2"/>
+        <cfvo type="num" val="2.5"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D57984A-85A0-446F-8653-A3FA379F8EE5}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11350,10 +14557,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>63</v>
       </c>
     </row>
